--- a/deploy/demo/documents/exercise-northwind-logistics.xlsx
+++ b/deploy/demo/documents/exercise-northwind-logistics.xlsx
@@ -196,7 +196,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
     <oddHeader>&amp;LExercise NORTHWIND 26 - fictional</oddHeader>
-    <oddFooter>&amp;RFictional workbook for demonstration purposes</oddFooter>
+    <oddFooter>&amp;RFictional workbook</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
--- a/deploy/demo/documents/exercise-northwind-logistics.xlsx
+++ b/deploy/demo/documents/exercise-northwind-logistics.xlsx
@@ -194,6 +194,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape"/>
   <headerFooter>
     <oddHeader>&amp;LExercise NORTHWIND 26 - fictional</oddHeader>
     <oddFooter>&amp;RFictional workbook</oddFooter>
